--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_27.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_27.xlsx
@@ -471,292 +471,292 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87696</v>
+        <v>96235</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gabriela Peixoto</t>
+          <t>Ana Lívia Melo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45081</v>
+        <v>45084</v>
       </c>
       <c r="G2" t="n">
-        <v>4046.88</v>
+        <v>4144.29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>43661</v>
+        <v>66425</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cauã da Mota</t>
+          <t>Rafael da Mata</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45084</v>
+        <v>45087</v>
       </c>
       <c r="G3" t="n">
-        <v>4178.95</v>
+        <v>12176.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6063</v>
+        <v>79215</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ana Júlia da Rosa</t>
+          <t>Sra. Cecília Nunes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>6</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45104</v>
+        <v>45082</v>
       </c>
       <c r="G4" t="n">
-        <v>6145.04</v>
+        <v>5679.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>39448</v>
+        <v>62818</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sophia Viana</t>
+          <t>Gustavo Henrique Castro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45081</v>
+        <v>45099</v>
       </c>
       <c r="G5" t="n">
-        <v>10434.8</v>
+        <v>5836.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20097</v>
+        <v>47082</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camila Rodrigues</t>
+          <t>Melissa Correia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>45098</v>
       </c>
       <c r="G6" t="n">
-        <v>7294.41</v>
+        <v>10489.42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>90626</v>
+        <v>15089</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rafael Ribeiro</t>
+          <t>Arthur Rocha</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45081</v>
+        <v>45098</v>
       </c>
       <c r="G7" t="n">
-        <v>8708.360000000001</v>
+        <v>10717.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96695</v>
+        <v>33604</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nathan Barros</t>
+          <t>Maria Julia Farias</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>7</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45096</v>
+        <v>45095</v>
       </c>
       <c r="G8" t="n">
-        <v>11772.59</v>
+        <v>9270.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>39170</v>
+        <v>39826</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kevin da Cunha</t>
+          <t>Ana Luiza Nogueira</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45097</v>
+        <v>45078</v>
       </c>
       <c r="G9" t="n">
-        <v>5022.01</v>
+        <v>2878.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11102</v>
+        <v>88758</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sabrina Nascimento</t>
+          <t>Isaac Silveira</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45079</v>
+        <v>45095</v>
       </c>
       <c r="G10" t="n">
-        <v>11625.68</v>
+        <v>7263.31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>47568</v>
+        <v>10769</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dr. Luiz Gustavo Cardoso</t>
+          <t>Bryan Costela</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45104</v>
+        <v>45105</v>
       </c>
       <c r="G11" t="n">
-        <v>12326.19</v>
+        <v>9888.65</v>
       </c>
     </row>
   </sheetData>
